--- a/docs/reference/srd_Creatures_Trimmed_V4.xlsx
+++ b/docs/reference/srd_Creatures_Trimmed_V4.xlsx
@@ -8887,7 +8887,7 @@
       </c>
       <c r="R98" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
@@ -9063,7 +9063,7 @@
       </c>
       <c r="R100" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
@@ -9943,7 +9943,7 @@
       </c>
       <c r="R110" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
@@ -10647,7 +10647,7 @@
       </c>
       <c r="R118" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
@@ -12495,7 +12495,7 @@
       </c>
       <c r="R139" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
@@ -12583,7 +12583,7 @@
       </c>
       <c r="R140" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
@@ -23763,32 +23763,19 @@
         </is>
       </c>
     </row>
-    <row r="268">
-    </row>
-    <row r="269">
-    </row>
-    <row r="270">
-    </row>
-    <row r="271">
-    </row>
-    <row r="272">
-    </row>
-    <row r="273">
-    </row>
-    <row r="274">
-    </row>
-    <row r="275">
-    </row>
-    <row r="276">
-    </row>
-    <row r="277">
-    </row>
-    <row r="278">
-    </row>
-    <row r="279">
-    </row>
-    <row r="280">
-    </row>
+    <row r="268"/>
+    <row r="269"/>
+    <row r="270"/>
+    <row r="271"/>
+    <row r="272"/>
+    <row r="273"/>
+    <row r="274"/>
+    <row r="275"/>
+    <row r="276"/>
+    <row r="277"/>
+    <row r="278"/>
+    <row r="279"/>
+    <row r="280"/>
     <row r="281">
       <c r="A281" t="inlineStr">
         <is>

--- a/docs/reference/srd_Creatures_Trimmed_V4.xlsx
+++ b/docs/reference/srd_Creatures_Trimmed_V4.xlsx
@@ -260,7 +260,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R287"/>
+  <dimension ref="A1:R290"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -24384,6 +24384,261 @@
         </is>
       </c>
     </row>
+    <row r="288">
+      <c r="A288" t="inlineStr">
+        <is>
+          <t>Bard</t>
+        </is>
+      </c>
+      <c r="B288" t="n">
+        <v>2</v>
+      </c>
+      <c r="C288" t="inlineStr">
+        <is>
+          <t>Humanoid (Bard)</t>
+        </is>
+      </c>
+      <c r="D288" t="inlineStr">
+        <is>
+          <t>Non-SRD Priority Targets</t>
+        </is>
+      </c>
+      <c r="F288" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="G288" t="inlineStr">
+        <is>
+          <t>30 ft.</t>
+        </is>
+      </c>
+      <c r="H288" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I288" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="J288" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K288" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L288" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="M288" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N288" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="O288" t="inlineStr">
+        <is>
+          <t>Yes - MotM/Volo-style magical NPC; confirm exact action model during implementation.</t>
+        </is>
+      </c>
+      <c r="P288" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="Q288" t="inlineStr">
+        <is>
+          <t>https://www.aidedd.org/dnd/monstres.php?vo=bard</t>
+        </is>
+      </c>
+      <c r="R288" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="289">
+      <c r="A289" t="inlineStr">
+        <is>
+          <t>Hobgoblin Devastator</t>
+        </is>
+      </c>
+      <c r="B289" t="n">
+        <v>4</v>
+      </c>
+      <c r="C289" t="inlineStr">
+        <is>
+          <t>Fey (Goblinoid)</t>
+        </is>
+      </c>
+      <c r="D289" t="inlineStr">
+        <is>
+          <t>Non-SRD Priority Targets</t>
+        </is>
+      </c>
+      <c r="F289" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="G289" t="inlineStr">
+        <is>
+          <t>30 ft.</t>
+        </is>
+      </c>
+      <c r="H289" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I289" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="J289" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K289" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L289" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="M289" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N289" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="O289" t="inlineStr">
+        <is>
+          <t>Yes - Uses magical ranged offense and spellcasting; confirm exact action model during implementation.</t>
+        </is>
+      </c>
+      <c r="P289" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="Q289" t="inlineStr">
+        <is>
+          <t>https://www.aidedd.org/dnd/monstres.php?vo=hobgoblin-devastator</t>
+        </is>
+      </c>
+      <c r="R289" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="290">
+      <c r="A290" t="inlineStr">
+        <is>
+          <t>Flameskull</t>
+        </is>
+      </c>
+      <c r="B290" t="n">
+        <v>4</v>
+      </c>
+      <c r="C290" t="inlineStr">
+        <is>
+          <t>Undead</t>
+        </is>
+      </c>
+      <c r="D290" t="inlineStr">
+        <is>
+          <t>Non-SRD Priority Targets</t>
+        </is>
+      </c>
+      <c r="F290" t="inlineStr">
+        <is>
+          <t>Tiny</t>
+        </is>
+      </c>
+      <c r="G290" t="inlineStr">
+        <is>
+          <t>0 ft., Fly 40 ft. (hover)</t>
+        </is>
+      </c>
+      <c r="H290" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I290" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="J290" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K290" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="L290" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="M290" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="N290" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="O290" t="inlineStr">
+        <is>
+          <t>Yes - The flameskull uses Fire Ray twice.</t>
+        </is>
+      </c>
+      <c r="P290" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="Q290" t="inlineStr">
+        <is>
+          <t>https://www.aidedd.org/dnd/monstres.php?vo=flameskull</t>
+        </is>
+      </c>
+      <c r="R290" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/docs/reference/srd_Creatures_Trimmed_V4.xlsx
+++ b/docs/reference/srd_Creatures_Trimmed_V4.xlsx
@@ -22791,7 +22791,7 @@
       </c>
       <c r="R256" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
@@ -23763,19 +23763,6 @@
         </is>
       </c>
     </row>
-    <row r="268"/>
-    <row r="269"/>
-    <row r="270"/>
-    <row r="271"/>
-    <row r="272"/>
-    <row r="273"/>
-    <row r="274"/>
-    <row r="275"/>
-    <row r="276"/>
-    <row r="277"/>
-    <row r="278"/>
-    <row r="279"/>
-    <row r="280"/>
     <row r="281">
       <c r="A281" t="inlineStr">
         <is>

--- a/docs/reference/srd_Creatures_Trimmed_V4.xlsx
+++ b/docs/reference/srd_Creatures_Trimmed_V4.xlsx
@@ -17863,7 +17863,7 @@
       </c>
       <c r="R200" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>

--- a/docs/reference/srd_Creatures_Trimmed_V4.xlsx
+++ b/docs/reference/srd_Creatures_Trimmed_V4.xlsx
@@ -18215,7 +18215,7 @@
       </c>
       <c r="R204" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>

--- a/docs/reference/srd_Creatures_Trimmed_V4.xlsx
+++ b/docs/reference/srd_Creatures_Trimmed_V4.xlsx
@@ -11791,7 +11791,7 @@
       </c>
       <c r="R131" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>

--- a/docs/reference/srd_Creatures_Trimmed_V4.xlsx
+++ b/docs/reference/srd_Creatures_Trimmed_V4.xlsx
@@ -9855,7 +9855,7 @@
       </c>
       <c r="R109" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>

--- a/docs/reference/srd_Creatures_Trimmed_V4.xlsx
+++ b/docs/reference/srd_Creatures_Trimmed_V4.xlsx
@@ -23671,7 +23671,7 @@
       </c>
       <c r="R266" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>

--- a/docs/reference/srd_Creatures_Trimmed_V4.xlsx
+++ b/docs/reference/srd_Creatures_Trimmed_V4.xlsx
@@ -23495,7 +23495,7 @@
       </c>
       <c r="R264" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>

--- a/docs/reference/srd_Creatures_Trimmed_V4.xlsx
+++ b/docs/reference/srd_Creatures_Trimmed_V4.xlsx
@@ -23759,7 +23759,7 @@
       </c>
       <c r="R267" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>

--- a/docs/reference/srd_Creatures_Trimmed_V4.xlsx
+++ b/docs/reference/srd_Creatures_Trimmed_V4.xlsx
@@ -23407,7 +23407,7 @@
       </c>
       <c r="R263" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>

--- a/docs/reference/srd_Creatures_Trimmed_V4.xlsx
+++ b/docs/reference/srd_Creatures_Trimmed_V4.xlsx
@@ -23583,7 +23583,7 @@
       </c>
       <c r="R265" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>

--- a/docs/reference/srd_Creatures_Trimmed_V4.xlsx
+++ b/docs/reference/srd_Creatures_Trimmed_V4.xlsx
@@ -23319,7 +23319,7 @@
       </c>
       <c r="R262" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>

--- a/docs/reference/srd_Creatures_Trimmed_V4.xlsx
+++ b/docs/reference/srd_Creatures_Trimmed_V4.xlsx
@@ -19359,7 +19359,7 @@
       </c>
       <c r="R217" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>

--- a/docs/reference/srd_Creatures_Trimmed_V4.xlsx
+++ b/docs/reference/srd_Creatures_Trimmed_V4.xlsx
@@ -5543,7 +5543,7 @@
       </c>
       <c r="R60" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>

--- a/docs/reference/srd_Creatures_Trimmed_V4.xlsx
+++ b/docs/reference/srd_Creatures_Trimmed_V4.xlsx
@@ -2551,7 +2551,7 @@
       </c>
       <c r="R26" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>

--- a/docs/reference/srd_Creatures_Trimmed_V4.xlsx
+++ b/docs/reference/srd_Creatures_Trimmed_V4.xlsx
@@ -1319,7 +1319,7 @@
       </c>
       <c r="R12" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>

--- a/docs/reference/srd_Creatures_Trimmed_V4.xlsx
+++ b/docs/reference/srd_Creatures_Trimmed_V4.xlsx
@@ -439,7 +439,7 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
